--- a/PPP_empirical_reinforcement_bundle_20260416_unified_v3/02_leave_one_province_out_jackknife/tables/leave_one_province_out_results.xlsx
+++ b/PPP_empirical_reinforcement_bundle_20260416_unified_v3/02_leave_one_province_out_jackknife/tables/leave_one_province_out_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_province" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_province" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,19 +506,19 @@
         <v>256</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3536714079042111</v>
+        <v>0.3536714079041875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09892707869056994</v>
+        <v>0.09892715334841821</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00125070730438497</v>
+        <v>0.001250716227348221</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.001956296848429739</v>
+        <v>-0.001956296848453332</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001956296848429739</v>
+        <v>0.001956296848453332</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -547,19 +547,19 @@
         <v>254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3535095811554431</v>
+        <v>0.3535095811553971</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1072771680002823</v>
+        <v>0.1072771666199802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002598289869475827</v>
+        <v>0.002598289585268272</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.002118123597197763</v>
+        <v>-0.002118123597243726</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002118123597197763</v>
+        <v>0.002118123597243726</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -588,19 +588,19 @@
         <v>253</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3751658027722716</v>
+        <v>0.3751658027722916</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09581946853830395</v>
+        <v>0.09581945677865679</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005032199211856544</v>
+        <v>0.0005032192674120673</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0195380980196308</v>
+        <v>0.01953809801965078</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0195380980196308</v>
+        <v>0.01953809801965078</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -629,19 +629,19 @@
         <v>253</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3459563076812611</v>
+        <v>0.3459563076812567</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09997748116529453</v>
+        <v>0.0999775893701168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001691634278174179</v>
+        <v>0.001691650874480359</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.009671397071379761</v>
+        <v>-0.009671397071384147</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009671397071379761</v>
+        <v>0.009671397071384147</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -670,19 +670,19 @@
         <v>253</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3625514387937789</v>
+        <v>0.3625514387937638</v>
       </c>
       <c r="F6" t="n">
-        <v>0.119529448904512</v>
+        <v>0.1195295002870512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005061670439806619</v>
+        <v>0.005061686976417391</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006923734041138052</v>
+        <v>0.006923734041123009</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006923734041138052</v>
+        <v>0.006923734041123009</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -711,19 +711,19 @@
         <v>253</v>
       </c>
       <c r="E7" t="n">
-        <v>0.343955813357267</v>
+        <v>0.3439558133573034</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1064710119730991</v>
+        <v>0.1064709911821774</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003069234968220469</v>
+        <v>0.003069230006252444</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01167189139537383</v>
+        <v>-0.01167189139533747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01167189139537383</v>
+        <v>0.01167189139533747</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -752,19 +752,19 @@
         <v>255</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3968241779805779</v>
+        <v>0.3968241779804846</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1108169812667112</v>
+        <v>0.1108169587380286</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001231585928705222</v>
+        <v>0.00123158355685482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04119647322793707</v>
+        <v>0.04119647322784381</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04119647322793707</v>
+        <v>0.04119647322784381</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -793,19 +793,19 @@
         <v>255</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3656428137099456</v>
+        <v>0.3656428137099472</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1167930899847055</v>
+        <v>0.1167930775139419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003958535488920522</v>
+        <v>0.003958532134610908</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01001510895730479</v>
+        <v>0.0100151089573064</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01001510895730479</v>
+        <v>0.0100151089573064</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -834,19 +834,19 @@
         <v>253</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3636836832432436</v>
+        <v>0.3636836832431993</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1072343153913532</v>
+        <v>0.1072342390948328</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002024916218873023</v>
+        <v>0.002024903496997027</v>
       </c>
       <c r="H10" t="n">
-        <v>0.008055978490602744</v>
+        <v>0.008055978490558446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008055978490602744</v>
+        <v>0.008055978490558446</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -875,19 +875,19 @@
         <v>253</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3529846447214663</v>
+        <v>0.3529846447215236</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1021863595664497</v>
+        <v>0.1021863510773431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001718515032330815</v>
+        <v>0.001718513741110747</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.002643060031174538</v>
+        <v>-0.00264306003111725</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002643060031174538</v>
+        <v>0.00264306003111725</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -916,19 +916,19 @@
         <v>253</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3669413397833248</v>
+        <v>0.3669413397833781</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1073064135531037</v>
+        <v>0.1073064577059005</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001881980966736765</v>
+        <v>0.001881987878777826</v>
       </c>
       <c r="H12" t="n">
-        <v>0.011313635030684</v>
+        <v>0.01131363503073729</v>
       </c>
       <c r="I12" t="n">
-        <v>0.011313635030684</v>
+        <v>0.01131363503073729</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -957,19 +957,19 @@
         <v>253</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3688650731478619</v>
+        <v>0.3688650731478976</v>
       </c>
       <c r="F13" t="n">
-        <v>0.101644177568871</v>
+        <v>0.1016442233069787</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001084217601489298</v>
+        <v>0.001084222302246375</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01323736839522111</v>
+        <v>0.0132373683952568</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01323736839522111</v>
+        <v>0.0132373683952568</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -998,19 +998,19 @@
         <v>253</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3721221000287187</v>
+        <v>0.372122100028634</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09976243393828661</v>
+        <v>0.09976241321460361</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008281789101451153</v>
+        <v>0.0008281771943198284</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01649439527607788</v>
+        <v>0.01649439527599317</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01649439527607788</v>
+        <v>0.01649439527599317</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1039,19 +1039,19 @@
         <v>253</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4345081870376275</v>
+        <v>0.4345081870376022</v>
       </c>
       <c r="F15" t="n">
-        <v>0.116709234631814</v>
+        <v>0.1167092117817176</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0008440135375900974</v>
+        <v>0.0008440118934020093</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07888048228498667</v>
+        <v>0.07888048228496136</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07888048228498667</v>
+        <v>0.07888048228496136</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1080,19 +1080,19 @@
         <v>253</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3549591218934142</v>
+        <v>0.3549591218934248</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1005335356721464</v>
+        <v>0.1005335131911125</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00140592590250637</v>
+        <v>0.001405922977528101</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0006685828592266074</v>
+        <v>-0.0006685828592160603</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0006685828592266074</v>
+        <v>0.0006685828592160603</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1121,19 +1121,19 @@
         <v>253</v>
       </c>
       <c r="E17" t="n">
-        <v>0.266830239314566</v>
+        <v>0.2668302393145768</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2782984685932532</v>
+        <v>0.2782983469313214</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3455896555421174</v>
+        <v>0.3455894479228062</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08879746543807482</v>
+        <v>-0.08879746543806405</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08879746543807482</v>
+        <v>0.08879746543806405</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>253</v>
       </c>
       <c r="E18" t="n">
-        <v>0.340968498584873</v>
+        <v>0.3409684985848432</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09810020750010913</v>
+        <v>0.09810027228666669</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001624815329973351</v>
+        <v>0.001624825113035934</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01465920616776784</v>
+        <v>-0.01465920616779759</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01465920616776784</v>
+        <v>0.01465920616779759</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -1203,19 +1203,19 @@
         <v>253</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3547616870988525</v>
+        <v>0.3547616870988385</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1037235054731973</v>
+        <v>0.1037235441693755</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001878557981517498</v>
+        <v>0.001878564238857946</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.000866017653788298</v>
+        <v>-0.0008660176538022868</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000866017653788298</v>
+        <v>0.0008660176538022868</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -1244,19 +1244,19 @@
         <v>253</v>
       </c>
       <c r="E20" t="n">
-        <v>0.338301460606162</v>
+        <v>0.338301460606224</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1041573361060755</v>
+        <v>0.1041572237921769</v>
       </c>
       <c r="G20" t="n">
-        <v>0.002934703598522535</v>
+        <v>0.0029346772094791</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.01732624414647888</v>
+        <v>-0.01732624414641681</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01732624414647888</v>
+        <v>0.01732624414641681</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1285,19 +1285,19 @@
         <v>253</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3630299998824726</v>
+        <v>0.3630299998824896</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1010202395129429</v>
+        <v>0.1010202136051395</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001190751321298499</v>
+        <v>0.001190748415257542</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00740229512983176</v>
+        <v>0.007402295129848802</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00740229512983176</v>
+        <v>0.007402295129848802</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -1326,19 +1326,19 @@
         <v>253</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3558691598425036</v>
+        <v>0.3558691598424812</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1075382529257758</v>
+        <v>0.1075382447060475</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002506437083595919</v>
+        <v>0.002506435445763615</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0002414550898627299</v>
+        <v>0.0002414550898403589</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0002414550898627299</v>
+        <v>0.0002414550898403589</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -1367,19 +1367,19 @@
         <v>254</v>
       </c>
       <c r="E23" t="n">
-        <v>0.36184137353338</v>
+        <v>0.3618413735334478</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09120506604897967</v>
+        <v>0.09120508486799056</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004371362529432372</v>
+        <v>0.0004371372230889892</v>
       </c>
       <c r="H23" t="n">
-        <v>0.006213668780739146</v>
+        <v>0.00621366878080698</v>
       </c>
       <c r="I23" t="n">
-        <v>0.006213668780739146</v>
+        <v>0.00621366878080698</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -1408,19 +1408,19 @@
         <v>253</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3744558826709926</v>
+        <v>0.3744558826709649</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09187396829790102</v>
+        <v>0.09187402297808826</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0003255576655936991</v>
+        <v>0.000325559817668619</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01882817791835173</v>
+        <v>0.01882817791832408</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01882817791835173</v>
+        <v>0.01882817791832408</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -1449,19 +1449,19 @@
         <v>253</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3539046861989025</v>
+        <v>0.3539046861988569</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1025355677293664</v>
+        <v>0.102535583632615</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001731120325754706</v>
+        <v>0.001731122751583423</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.001723018553738298</v>
+        <v>-0.001723018553783928</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001723018553738298</v>
+        <v>0.001723018553783928</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -1490,19 +1490,19 @@
         <v>259</v>
       </c>
       <c r="E26" t="n">
-        <v>0.364471676931377</v>
+        <v>0.3644716769314263</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09658438795410637</v>
+        <v>0.0965843832984645</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0007370700520478261</v>
+        <v>0.0007370696925520114</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00884397217873617</v>
+        <v>0.00884397217878552</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00884397217873617</v>
+        <v>0.00884397217878552</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -1531,19 +1531,19 @@
         <v>253</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3672624808678267</v>
+        <v>0.3672624808678986</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1051013870482819</v>
+        <v>0.1051013556682281</v>
       </c>
       <c r="G27" t="n">
-        <v>0.00154719275009887</v>
+        <v>0.001547188509283037</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01163477611518587</v>
+        <v>0.01163477611525776</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01163477611518587</v>
+        <v>0.01163477611525776</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -1572,19 +1572,19 @@
         <v>253</v>
       </c>
       <c r="E28" t="n">
-        <v>0.341367213555335</v>
+        <v>0.3413672135553301</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1081680913865289</v>
+        <v>0.1081681290382788</v>
       </c>
       <c r="G28" t="n">
-        <v>0.003713172875710027</v>
+        <v>0.003713183244918854</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.01426049119730582</v>
+        <v>-0.01426049119731071</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01426049119730582</v>
+        <v>0.01426049119731071</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         <v>253</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3256383145175358</v>
+        <v>0.3256383145175124</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08925209836042489</v>
+        <v>0.08925203937658327</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001029367982357834</v>
+        <v>0.001029361383216222</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.029989390235105</v>
+        <v>-0.02998939023512848</v>
       </c>
       <c r="I29" t="n">
-        <v>0.029989390235105</v>
+        <v>0.02998939023512848</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -1654,19 +1654,19 @@
         <v>253</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3432472656469797</v>
+        <v>0.3432472656470105</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1050299440507452</v>
+        <v>0.1050299886254646</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002786914762392811</v>
+        <v>0.002786924707158981</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01238043910566111</v>
+        <v>-0.0123804391056303</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01238043910566111</v>
+        <v>0.0123804391056303</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -1695,19 +1695,19 @@
         <v>255</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3789302904598955</v>
+        <v>0.3789302904600154</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1047844947619134</v>
+        <v>0.1047844858650853</v>
       </c>
       <c r="G31" t="n">
-        <v>0.001121387031055458</v>
+        <v>0.001121386117740661</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02330258570725463</v>
+        <v>0.02330258570737453</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02330258570725463</v>
+        <v>0.02330258570737453</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -1736,19 +1736,19 @@
         <v>253</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3707928491272691</v>
+        <v>0.3707928491272579</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09791492406734448</v>
+        <v>0.0979148882852546</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0007112765463656907</v>
+        <v>0.0007112739048475052</v>
       </c>
       <c r="H32" t="n">
-        <v>0.01516514437462824</v>
+        <v>0.01516514437461708</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01516514437462824</v>
+        <v>0.01516514437461708</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -1777,19 +1777,19 @@
         <v>256</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4010087738818338</v>
+        <v>-0.4010087738818052</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1018381608387149</v>
+        <v>0.1018382381347179</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0004736739021998229</v>
+        <v>0.0004736777344004765</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001268712210875489</v>
+        <v>0.001268712210904133</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001268712210875489</v>
+        <v>0.001268712210904133</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -1818,19 +1818,19 @@
         <v>254</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.403280874995719</v>
+        <v>-0.4032808749956822</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1068246123803797</v>
+        <v>0.106824610944931</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0007339941096988001</v>
+        <v>0.0007339940098507801</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.001003388903009717</v>
+        <v>-0.001003388902972857</v>
       </c>
       <c r="I34" t="n">
-        <v>0.001003388903009717</v>
+        <v>0.001003388902972857</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -1859,19 +1859,19 @@
         <v>253</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4205222374078531</v>
+        <v>-0.4205222374078785</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09712731527139117</v>
+        <v>0.09712730321782782</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001624389625597513</v>
+        <v>0.0001624387224483678</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0182447513151438</v>
+        <v>-0.01824475131516923</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0182447513151438</v>
+        <v>0.01824475131516923</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>253</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3954865597943894</v>
+        <v>-0.3954865597943844</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1019438485439623</v>
+        <v>0.1019439615886488</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000554438005295034</v>
+        <v>0.0005544444412771924</v>
       </c>
       <c r="H36" t="n">
-        <v>0.006790926298319899</v>
+        <v>0.006790926298324895</v>
       </c>
       <c r="I36" t="n">
-        <v>0.006790926298319899</v>
+        <v>0.006790926298324895</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -1941,19 +1941,19 @@
         <v>253</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.433054567584618</v>
+        <v>-0.4330545675846016</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1203577123615918</v>
+        <v>0.1203577646318525</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00117687407489276</v>
+        <v>0.001176878946254899</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.03077708149190872</v>
+        <v>-0.03077708149189229</v>
       </c>
       <c r="I37" t="n">
-        <v>0.03077708149190872</v>
+        <v>0.03077708149189229</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -1982,19 +1982,19 @@
         <v>253</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.3920531485526891</v>
+        <v>-0.3920531485527314</v>
       </c>
       <c r="F38" t="n">
-        <v>0.107501115952707</v>
+        <v>0.1075010943196555</v>
       </c>
       <c r="G38" t="n">
-        <v>0.001033631344861403</v>
+        <v>0.001033629328167444</v>
       </c>
       <c r="H38" t="n">
-        <v>0.01022433754002017</v>
+        <v>0.01022433753997787</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01022433754002017</v>
+        <v>0.01022433753997787</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>255</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.4451592038251281</v>
+        <v>-0.4451592038250239</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1171539038669258</v>
+        <v>0.1171538805047352</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0006870776191380905</v>
+        <v>0.0006870762208924189</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.04288171773241883</v>
+        <v>-0.04288171773231464</v>
       </c>
       <c r="I39" t="n">
-        <v>0.04288171773241883</v>
+        <v>0.04288171773231464</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -2064,19 +2064,19 @@
         <v>255</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.4106885911517283</v>
+        <v>-0.4106885911517301</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1215305929092544</v>
+        <v>0.1215305799121749</v>
       </c>
       <c r="G40" t="n">
-        <v>0.002090144747865578</v>
+        <v>0.002090142783327841</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.008411105059018986</v>
+        <v>-0.008411105059020818</v>
       </c>
       <c r="I40" t="n">
-        <v>0.008411105059018986</v>
+        <v>0.008411105059020818</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -2105,19 +2105,19 @@
         <v>253</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.4088701709835382</v>
+        <v>-0.4088701709834888</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1088832808687435</v>
+        <v>0.1088832018128366</v>
       </c>
       <c r="G41" t="n">
-        <v>0.000774500897572403</v>
+        <v>0.0007744952422177841</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.00659268489082887</v>
+        <v>-0.006592684890779521</v>
       </c>
       <c r="I41" t="n">
-        <v>0.00659268489082887</v>
+        <v>0.006592684890779521</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -2146,19 +2146,19 @@
         <v>253</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.4006945778112342</v>
+        <v>-0.4006945778112979</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1071361276735065</v>
+        <v>0.1071361190965533</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0008063890875222527</v>
+        <v>0.0008063884415164165</v>
       </c>
       <c r="H42" t="n">
-        <v>0.001582908281475059</v>
+        <v>0.001582908281411388</v>
       </c>
       <c r="I42" t="n">
-        <v>0.001582908281475059</v>
+        <v>0.001582908281411388</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -2187,19 +2187,19 @@
         <v>253</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.4069166741681475</v>
+        <v>-0.4069166741682083</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1081709268774387</v>
+        <v>0.1081709728584543</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000760785860385453</v>
+        <v>0.0007607891199074922</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.004639188075438172</v>
+        <v>-0.004639188075498957</v>
       </c>
       <c r="I43" t="n">
-        <v>0.004639188075438172</v>
+        <v>0.004639188075498957</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -2228,19 +2228,19 @@
         <v>253</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.4126329433575353</v>
+        <v>-0.4126329433575741</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1014959145973994</v>
+        <v>0.1014959628276645</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0003347711107292557</v>
+        <v>0.0003347728723769396</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.01035545726482601</v>
+        <v>-0.01035545726486481</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01035545726482601</v>
+        <v>0.01035545726486481</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -2269,19 +2269,19 @@
         <v>253</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4166301617006296</v>
+        <v>-0.416630161700534</v>
       </c>
       <c r="F45" t="n">
-        <v>0.09676941269963391</v>
+        <v>0.09676939125939805</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0001736206004773674</v>
+        <v>0.0001736201451992655</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.01435267560792031</v>
+        <v>-0.01435267560782466</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01435267560792031</v>
+        <v>0.01435267560782466</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -2310,19 +2310,19 @@
         <v>253</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4661525164563906</v>
+        <v>-0.4661525164563604</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1098399377362118</v>
+        <v>0.1098399070698475</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0002055458866083569</v>
+        <v>0.0002055452184846015</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.06387503036368131</v>
+        <v>-0.06387503036365111</v>
       </c>
       <c r="I46" t="n">
-        <v>0.06387503036368131</v>
+        <v>0.06387503036365111</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -2351,19 +2351,19 @@
         <v>253</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.3999030744566801</v>
+        <v>-0.3999030744566949</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1025468650840596</v>
+        <v>0.1025468418200917</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0005249312945372367</v>
+        <v>0.0005249300399946392</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00237441163602925</v>
+        <v>0.002374411636014373</v>
       </c>
       <c r="I47" t="n">
-        <v>0.00237441163602925</v>
+        <v>0.002374411636014373</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
@@ -2392,19 +2392,19 @@
         <v>253</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2323783209330787</v>
+        <v>-0.232378320933089</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1932352692465455</v>
+        <v>0.1932352187557794</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2388711159791991</v>
+        <v>0.2388709961914585</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1698991651596306</v>
+        <v>0.1698991651596203</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1698991651596306</v>
+        <v>0.1698991651596203</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -2433,19 +2433,19 @@
         <v>253</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3886254630593137</v>
+        <v>-0.3886254630592781</v>
       </c>
       <c r="F49" t="n">
-        <v>0.09716605254932775</v>
+        <v>0.09716611987877034</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0004004973918000829</v>
+        <v>0.0004005004058433285</v>
       </c>
       <c r="H49" t="n">
-        <v>0.01365202303339558</v>
+        <v>0.01365202303343116</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01365202303339558</v>
+        <v>0.01365202303343116</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -2474,19 +2474,19 @@
         <v>253</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4021643132885493</v>
+        <v>-0.4021643132885364</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1030413175988513</v>
+        <v>0.1030413577181334</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0005203678662647637</v>
+        <v>0.0005203700028079674</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0001131728041599556</v>
+        <v>0.0001131728041728897</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0001131728041599556</v>
+        <v>0.0001131728041728897</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -2515,19 +2515,19 @@
         <v>253</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.389769894027485</v>
+        <v>-0.3897698940275599</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1055506900075027</v>
+        <v>0.1055505749663576</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0009150561326126444</v>
+        <v>0.0009150463101137413</v>
       </c>
       <c r="H51" t="n">
-        <v>0.01250759206522434</v>
+        <v>0.0125075920651494</v>
       </c>
       <c r="I51" t="n">
-        <v>0.01250759206522434</v>
+        <v>0.0125075920651494</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -2556,19 +2556,19 @@
         <v>253</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.4155943233236507</v>
+        <v>-0.4155943233236689</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1014296014972519</v>
+        <v>0.1014295740684451</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0003069297980471166</v>
+        <v>0.0003069288704083515</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0133168372309414</v>
+        <v>-0.01331683723095956</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0133168372309414</v>
+        <v>0.01331683723095956</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -2597,19 +2597,19 @@
         <v>253</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.4119340716329422</v>
+        <v>-0.4119340716329169</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1082465172166206</v>
+        <v>0.1082465089064806</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0006765707605051721</v>
+        <v>0.0006765702294535058</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.009656585540232909</v>
+        <v>-0.009656585540207596</v>
       </c>
       <c r="I53" t="n">
-        <v>0.009656585540232909</v>
+        <v>0.009656585540207596</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -2638,19 +2638,19 @@
         <v>254</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4060498800579872</v>
+        <v>-0.4060498800580636</v>
       </c>
       <c r="F54" t="n">
-        <v>0.09400939646138316</v>
+        <v>0.09400941616282282</v>
       </c>
       <c r="G54" t="n">
-        <v>0.000167130013071841</v>
+        <v>0.0001671304291274312</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.003772393965277898</v>
+        <v>-0.003772393965354337</v>
       </c>
       <c r="I54" t="n">
-        <v>0.003772393965277898</v>
+        <v>0.003772393965354337</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -2679,19 +2679,19 @@
         <v>253</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4185198552218774</v>
+        <v>-0.4185198552218449</v>
       </c>
       <c r="F55" t="n">
-        <v>0.09658468950634246</v>
+        <v>0.09658474718225046</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0001608414166337067</v>
+        <v>0.0001608425617293111</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0162423691291681</v>
+        <v>-0.01624236912913557</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0162423691291681</v>
+        <v>0.01624236912913557</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -2720,19 +2720,19 @@
         <v>253</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3959458989939604</v>
+        <v>-0.3959458989939103</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1020783825188958</v>
+        <v>0.1020783989082415</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0005553559184262516</v>
+        <v>0.0005553568516525408</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00633158709874887</v>
+        <v>0.006331587098798996</v>
       </c>
       <c r="I56" t="n">
-        <v>0.00633158709874887</v>
+        <v>0.006331587098798996</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>259</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4111655990626778</v>
+        <v>-0.4111655990627336</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1023479634947482</v>
+        <v>0.1023479586068545</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0003816651132293937</v>
+        <v>0.0003816649142183884</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.008888112969968498</v>
+        <v>-0.008888112970024287</v>
       </c>
       <c r="I57" t="n">
-        <v>0.008888112969968498</v>
+        <v>0.008888112970024287</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -2802,19 +2802,19 @@
         <v>253</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4004781481783897</v>
+        <v>-0.4004781481784684</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1019799294909664</v>
+        <v>0.1019798960155575</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000487560148900811</v>
+        <v>0.0004875584485634027</v>
       </c>
       <c r="H58" t="n">
-        <v>0.001799337914319576</v>
+        <v>0.001799337914240917</v>
       </c>
       <c r="I58" t="n">
-        <v>0.001799337914319576</v>
+        <v>0.001799337914240917</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -2843,19 +2843,19 @@
         <v>253</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3902276019439657</v>
+        <v>-0.3902276019439616</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1078820488918031</v>
+        <v>0.107882088859887</v>
       </c>
       <c r="G59" t="n">
-        <v>0.001118751894619421</v>
+        <v>0.00111875587164986</v>
       </c>
       <c r="H59" t="n">
-        <v>0.01204988414874358</v>
+        <v>0.01204988414874775</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01204988414874358</v>
+        <v>0.01204988414874775</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -2884,19 +2884,19 @@
         <v>253</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3736040912146258</v>
+        <v>-0.3736040912146005</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09007827616051867</v>
+        <v>0.0900782134385</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0002676267927793581</v>
+        <v>0.000267624680156311</v>
       </c>
       <c r="H60" t="n">
-        <v>0.02867339487808351</v>
+        <v>0.02867339487810877</v>
       </c>
       <c r="I60" t="n">
-        <v>0.02867339487808351</v>
+        <v>0.02867339487810877</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -2925,19 +2925,19 @@
         <v>253</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3875595038230257</v>
+        <v>-0.3875595038230609</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1052236184299499</v>
+        <v>0.1052236654276216</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0009386004473306138</v>
+        <v>0.0009386045628087898</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01471798226968357</v>
+        <v>0.01471798226964838</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01471798226968357</v>
+        <v>0.01471798226964838</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -2966,19 +2966,19 @@
         <v>255</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4415474881472929</v>
+        <v>-0.4415474881474338</v>
       </c>
       <c r="F62" t="n">
-        <v>0.107696709697668</v>
+        <v>0.1076967002741809</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0003048030280713403</v>
+        <v>0.0003048027297764868</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.03927000205458359</v>
+        <v>-0.03927000205472447</v>
       </c>
       <c r="I62" t="n">
-        <v>0.03927000205458359</v>
+        <v>0.03927000205472447</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -3007,19 +3007,19 @@
         <v>253</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4170620745149117</v>
+        <v>-0.4170620745149008</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09938734870904811</v>
+        <v>0.09938731115131395</v>
       </c>
       <c r="G63" t="n">
-        <v>0.000234189205953669</v>
+        <v>0.0002341881889285431</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.01478458842220243</v>
+        <v>-0.01478458842219155</v>
       </c>
       <c r="I63" t="n">
-        <v>0.01478458842220243</v>
+        <v>0.01478458842219155</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -3048,19 +3048,19 @@
         <v>256</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5182820411531712</v>
+        <v>0.5182820411531374</v>
       </c>
       <c r="F64" t="n">
-        <v>0.455158012615509</v>
+        <v>0.4551578809989232</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2641535821561008</v>
+        <v>0.2641534470081179</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.007014894442228248</v>
+        <v>-0.00701489444226211</v>
       </c>
       <c r="I64" t="n">
-        <v>0.007014894442228248</v>
+        <v>0.00701489444226211</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -3089,19 +3089,19 @@
         <v>254</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5098202608538768</v>
+        <v>0.5098202608537926</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4595740007683823</v>
+        <v>0.4595739988125511</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2764017209196629</v>
+        <v>0.276401718917579</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.0154766747415227</v>
+        <v>-0.01547667474160686</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0154766747415227</v>
+        <v>0.01547667474160686</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -3130,19 +3130,19 @@
         <v>253</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5565979238663473</v>
+        <v>0.5565979238663629</v>
       </c>
       <c r="F66" t="n">
-        <v>0.461723831824044</v>
+        <v>0.4617238419331046</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2377632180498472</v>
+        <v>0.2377632280767073</v>
       </c>
       <c r="H66" t="n">
-        <v>0.03130098827094785</v>
+        <v>0.03130098827096339</v>
       </c>
       <c r="I66" t="n">
-        <v>0.03130098827094785</v>
+        <v>0.03130098827096339</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -3171,19 +3171,19 @@
         <v>253</v>
       </c>
       <c r="E67" t="n">
-        <v>0.501505767413567</v>
+        <v>0.5015057674135582</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4611829810379243</v>
+        <v>0.4611828776245778</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2858010487526602</v>
+        <v>0.2858009428413721</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.02379116818183247</v>
+        <v>-0.02379116818184124</v>
       </c>
       <c r="I67" t="n">
-        <v>0.02379116818183247</v>
+        <v>0.02379116818184124</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -3212,19 +3212,19 @@
         <v>253</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3608547952472701</v>
+        <v>0.3608547952472708</v>
       </c>
       <c r="F68" t="n">
-        <v>0.32652605876086</v>
+        <v>0.3265260021628064</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2781866189083082</v>
+        <v>0.2781865372944607</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.1644421403481294</v>
+        <v>-0.1644421403481287</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1644421403481294</v>
+        <v>0.1644421403481287</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -3253,19 +3253,19 @@
         <v>253</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5021471312059836</v>
+        <v>0.502147131206036</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4620995324278495</v>
+        <v>0.462099554765574</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2861351719888975</v>
+        <v>0.2861351948235813</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.02314980438941583</v>
+        <v>-0.02314980438936343</v>
       </c>
       <c r="I69" t="n">
-        <v>0.02314980438941583</v>
+        <v>0.02314980438936343</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -3294,19 +3294,19 @@
         <v>255</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5696330594779605</v>
+        <v>0.5696330594778474</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4497508006574031</v>
+        <v>0.4497508412285383</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2153940911786419</v>
+        <v>0.2153941314809801</v>
       </c>
       <c r="H70" t="n">
-        <v>0.04433612388256103</v>
+        <v>0.0443361238824479</v>
       </c>
       <c r="I70" t="n">
-        <v>0.04433612388256103</v>
+        <v>0.0443361238824479</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -3335,19 +3335,19 @@
         <v>255</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5374299808082984</v>
+        <v>0.5374299808083045</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4507130569559398</v>
+        <v>0.450713065124729</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2427705324200189</v>
+        <v>0.2427705407581511</v>
       </c>
       <c r="H71" t="n">
-        <v>0.01213304521289893</v>
+        <v>0.01213304521290504</v>
       </c>
       <c r="I71" t="n">
-        <v>0.01213304521289893</v>
+        <v>0.01213304521290504</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -3376,19 +3376,19 @@
         <v>253</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5461135916042028</v>
+        <v>0.546113591604151</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4590330282635572</v>
+        <v>0.4590331037577816</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2438119977353322</v>
+        <v>0.2438120734663339</v>
       </c>
       <c r="H72" t="n">
-        <v>0.02081665600880334</v>
+        <v>0.02081665600875149</v>
       </c>
       <c r="I72" t="n">
-        <v>0.02081665600880334</v>
+        <v>0.02081665600875149</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -3417,19 +3417,19 @@
         <v>253</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5086428711140841</v>
+        <v>0.5086428711141476</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4328554042654127</v>
+        <v>0.4328554151310238</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2495181275811549</v>
+        <v>0.2495181391943462</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.01665406448131534</v>
+        <v>-0.01665406448125184</v>
       </c>
       <c r="I73" t="n">
-        <v>0.01665406448131534</v>
+        <v>0.01665406448125184</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -3458,19 +3458,19 @@
         <v>253</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5718605722223955</v>
+        <v>0.5718605722224612</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4598995741330778</v>
+        <v>0.4598995293240474</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2236620022393829</v>
+        <v>0.2236619582702568</v>
       </c>
       <c r="H74" t="n">
-        <v>0.04656363662699603</v>
+        <v>0.04656363662706176</v>
       </c>
       <c r="I74" t="n">
-        <v>0.04656363662699603</v>
+        <v>0.04656363662706176</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -3499,19 +3499,19 @@
         <v>253</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5705189887688997</v>
+        <v>0.5705189887689305</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4949958749485636</v>
+        <v>0.4949958226338296</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2584981571846725</v>
+        <v>0.258498107968233</v>
       </c>
       <c r="H75" t="n">
-        <v>0.04522205317350025</v>
+        <v>0.04522205317353101</v>
       </c>
       <c r="I75" t="n">
-        <v>0.04522205317350025</v>
+        <v>0.04522205317353101</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -3540,19 +3540,19 @@
         <v>253</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5710988143962586</v>
+        <v>0.5710988143961705</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4747998090188068</v>
+        <v>0.4747998295499014</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2387745214266555</v>
+        <v>0.238774541248812</v>
       </c>
       <c r="H76" t="n">
-        <v>0.04580187880085917</v>
+        <v>0.04580187880077102</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04580187880085917</v>
+        <v>0.04580187880077102</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -3581,19 +3581,19 @@
         <v>253</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5936506254034036</v>
+        <v>0.5936506254033883</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5590975914125672</v>
+        <v>0.5590976022658062</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2970887032430847</v>
+        <v>0.2970887124444622</v>
       </c>
       <c r="H77" t="n">
-        <v>0.06835368980800416</v>
+        <v>0.06835368980798884</v>
       </c>
       <c r="I77" t="n">
-        <v>0.06835368980800416</v>
+        <v>0.06835368980798884</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -3622,19 +3622,19 @@
         <v>253</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5278996927186964</v>
+        <v>0.5278996927187127</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4542642460721295</v>
+        <v>0.4542642668942262</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2546705772358354</v>
+        <v>0.2546705985242579</v>
       </c>
       <c r="H78" t="n">
-        <v>0.002602757123296939</v>
+        <v>0.00260275712331326</v>
       </c>
       <c r="I78" t="n">
-        <v>0.002602757123296939</v>
+        <v>0.00260275712331326</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
@@ -3663,19 +3663,19 @@
         <v>253</v>
       </c>
       <c r="E79" t="n">
-        <v>1.486312005015742</v>
+        <v>1.4863120050158</v>
       </c>
       <c r="F79" t="n">
-        <v>1.614288703486025</v>
+        <v>1.614288361222207</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3647915265913221</v>
+        <v>0.3647914263594286</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9610150694203422</v>
+        <v>0.9610150694204008</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9610150694203422</v>
+        <v>0.9610150694204008</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
@@ -3704,19 +3704,19 @@
         <v>253</v>
       </c>
       <c r="E80" t="n">
-        <v>0.50136154906258</v>
+        <v>0.5013615490625685</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4657361900863605</v>
+        <v>0.465736125735815</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2905812706533785</v>
+        <v>0.290581205284445</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.02393538653281946</v>
+        <v>-0.023935386532831</v>
       </c>
       <c r="I80" t="n">
-        <v>0.02393538653281946</v>
+        <v>0.023935386532831</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
@@ -3745,19 +3745,19 @@
         <v>253</v>
       </c>
       <c r="E81" t="n">
-        <v>0.515330518258174</v>
+        <v>0.5153305182581522</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4554667619448884</v>
+        <v>0.4554667209953516</v>
       </c>
       <c r="G81" t="n">
-        <v>0.267142365969105</v>
+        <v>0.267142323875182</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.009966417337225475</v>
+        <v>-0.009966417337247235</v>
       </c>
       <c r="I81" t="n">
-        <v>0.009966417337225475</v>
+        <v>0.009966417337247235</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -3786,19 +3786,19 @@
         <v>253</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4806113320509793</v>
+        <v>0.4806113320510427</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4464975561690647</v>
+        <v>0.446497671807979</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2906206156536977</v>
+        <v>0.290620738185653</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.04468560354442019</v>
+        <v>-0.0446856035443568</v>
       </c>
       <c r="I82" t="n">
-        <v>0.04468560354442019</v>
+        <v>0.0446856035443568</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -3827,19 +3827,19 @@
         <v>253</v>
       </c>
       <c r="E83" t="n">
-        <v>0.5204986486665929</v>
+        <v>0.5204986486666027</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4660361063709481</v>
+        <v>0.4660361376385601</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2732210611842819</v>
+        <v>0.2732210926998154</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.004798286928806572</v>
+        <v>-0.004798286928796802</v>
       </c>
       <c r="I83" t="n">
-        <v>0.004798286928806572</v>
+        <v>0.004798286928796802</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
@@ -3868,19 +3868,19 @@
         <v>253</v>
       </c>
       <c r="E84" t="n">
-        <v>0.4748820673494244</v>
+        <v>0.4748820673494047</v>
       </c>
       <c r="F84" t="n">
-        <v>0.4328426258850639</v>
+        <v>0.4328426352543085</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2816139544865325</v>
+        <v>0.2816139646935722</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.05041486824597508</v>
+        <v>-0.05041486824599473</v>
       </c>
       <c r="I84" t="n">
-        <v>0.05041486824597508</v>
+        <v>0.05041486824599473</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
@@ -3909,19 +3909,19 @@
         <v>254</v>
       </c>
       <c r="E85" t="n">
-        <v>0.5449413652318704</v>
+        <v>0.544941365231946</v>
       </c>
       <c r="F85" t="n">
-        <v>0.4586757340701617</v>
+        <v>0.458675714446628</v>
       </c>
       <c r="G85" t="n">
-        <v>0.2444430753065525</v>
+        <v>0.2444430555954402</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01964442963647095</v>
+        <v>0.01964442963654656</v>
       </c>
       <c r="I85" t="n">
-        <v>0.01964442963647095</v>
+        <v>0.01964442963654656</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
@@ -3950,19 +3950,19 @@
         <v>253</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5951581826274271</v>
+        <v>0.5951581826274011</v>
       </c>
       <c r="F86" t="n">
-        <v>0.4811501536945723</v>
+        <v>0.4811500793963448</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2260295362981432</v>
+        <v>0.2260294664258226</v>
       </c>
       <c r="H86" t="n">
-        <v>0.06986124703202767</v>
+        <v>0.06986124703200158</v>
       </c>
       <c r="I86" t="n">
-        <v>0.06986124703202767</v>
+        <v>0.06986124703200158</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
@@ -3991,19 +3991,19 @@
         <v>253</v>
       </c>
       <c r="E87" t="n">
-        <v>0.5277967113971369</v>
+        <v>0.5277967113970741</v>
       </c>
       <c r="F87" t="n">
-        <v>0.4521733241483231</v>
+        <v>0.4521733120296216</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2526200357584348</v>
+        <v>0.2526200233297929</v>
       </c>
       <c r="H87" t="n">
-        <v>0.002499775801737436</v>
+        <v>0.002499775801674597</v>
       </c>
       <c r="I87" t="n">
-        <v>0.002499775801737436</v>
+        <v>0.002499775801674597</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
@@ -4032,19 +4032,19 @@
         <v>259</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5199595955487719</v>
+        <v>0.5199595955488286</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4433813860086454</v>
+        <v>0.4433813895979644</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2504537491629512</v>
+        <v>0.2504537529108516</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.005337340046627559</v>
+        <v>-0.005337340046570827</v>
       </c>
       <c r="I88" t="n">
-        <v>0.005337340046627559</v>
+        <v>0.005337340046570827</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
@@ -4073,19 +4073,19 @@
         <v>253</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6061837939703179</v>
+        <v>0.6061837939704201</v>
       </c>
       <c r="F89" t="n">
-        <v>0.4594078466635693</v>
+        <v>0.4594078913515222</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1973285712410763</v>
+        <v>0.1973286135842205</v>
       </c>
       <c r="H89" t="n">
-        <v>0.08088685837491838</v>
+        <v>0.08088685837502063</v>
       </c>
       <c r="I89" t="n">
-        <v>0.08088685837491838</v>
+        <v>0.08088685837502063</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
@@ -4114,19 +4114,19 @@
         <v>253</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4987565688541573</v>
+        <v>0.4987565688541528</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4633913547105981</v>
+        <v>0.4633913171251056</v>
       </c>
       <c r="G90" t="n">
-        <v>0.2906578933129261</v>
+        <v>0.2906578549384717</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.02654036674124216</v>
+        <v>-0.02654036674124671</v>
       </c>
       <c r="I90" t="n">
-        <v>0.02654036674124216</v>
+        <v>0.02654036674124671</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
@@ -4155,19 +4155,19 @@
         <v>253</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4849737424903467</v>
+        <v>0.4849737424903166</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4642981809378022</v>
+        <v>0.464298242777426</v>
       </c>
       <c r="G91" t="n">
-        <v>0.3048690190662388</v>
+        <v>0.3048690823073036</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.04032319310505272</v>
+        <v>-0.04032319310508287</v>
       </c>
       <c r="I91" t="n">
-        <v>0.04032319310505272</v>
+        <v>0.04032319310508287</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
@@ -4196,19 +4196,19 @@
         <v>253</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5221428175691122</v>
+        <v>0.5221428175691523</v>
       </c>
       <c r="F92" t="n">
-        <v>0.4594712874322683</v>
+        <v>0.4594712406455496</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2650933762989568</v>
+        <v>0.2650933286809228</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.003154118026287289</v>
+        <v>-0.00315411802624721</v>
       </c>
       <c r="I92" t="n">
-        <v>0.003154118026287289</v>
+        <v>0.00315411802624721</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
@@ -4237,19 +4237,19 @@
         <v>255</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4800603529495046</v>
+        <v>0.4800603529496</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4560076158543122</v>
+        <v>0.4560076303457983</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3011503764739666</v>
+        <v>0.3011503915518585</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.04523658264589492</v>
+        <v>-0.04523658264579949</v>
       </c>
       <c r="I93" t="n">
-        <v>0.04523658264589492</v>
+        <v>0.04523658264579949</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
@@ -4278,19 +4278,19 @@
         <v>253</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2139394433788684</v>
+        <v>0.213939443378858</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2385781555242671</v>
+        <v>0.2385781168166</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3772487516165167</v>
+        <v>0.3772486752595057</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.311357492216531</v>
+        <v>-0.3113574922165415</v>
       </c>
       <c r="I94" t="n">
-        <v>0.311357492216531</v>
+        <v>0.3113574922165415</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0.0003845468522075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.266830239314566</v>
+        <v>0.2668302393145768</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4345081870376275</v>
+        <v>0.4345081870376022</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.08879746543807482</v>
+        <v>0.08879746543806405</v>
       </c>
     </row>
     <row r="3">
@@ -4432,10 +4432,10 @@
         <v>7.899841080299854e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4661525164563906</v>
+        <v>-0.4661525164563604</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2323783209330787</v>
+        <v>-0.232378320933089</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.1698991651596306</v>
+        <v>0.1698991651596203</v>
       </c>
     </row>
     <row r="4">
@@ -4473,10 +4473,10 @@
         <v>0.2125593654167483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2139394433788684</v>
+        <v>0.213939443378858</v>
       </c>
       <c r="G4" t="n">
-        <v>1.486312005015742</v>
+        <v>1.4863120050158</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.9610150694203422</v>
+        <v>0.9610150694204008</v>
       </c>
     </row>
   </sheetData>
